--- a/data/gravel/Esker Hayduke Ti 2025.xlsx
+++ b/data/gravel/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C9D566-DE0C-3247-91ED-432F0CFE7AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4368D46E-2E47-F843-8258-2564AD069FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -323,18 +323,12 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>Chainstay Length - Adjustable</t>
   </si>
   <si>
@@ -366,6 +360,15 @@
   </si>
   <si>
     <t>S4/XL</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>effectively equal to rigid fork of this length</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -785,7 +788,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="23">
@@ -796,7 +799,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -804,19 +807,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -984,7 +987,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3">
         <v>440</v>
@@ -999,16 +1002,16 @@
         <v>440</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1049,6 +1052,9 @@
       </c>
       <c r="F19" s="3">
         <v>495</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1317,7 +1323,7 @@
         <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1325,7 +1331,7 @@
         <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1378,8 +1384,8 @@
       <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>36</v>
+      <c r="B45" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1413,7 +1419,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1434,7 +1440,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1564,7 +1570,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Esker Hayduke Ti 2025.xlsx
+++ b/data/gravel/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4368D46E-2E47-F843-8258-2564AD069FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC373937-F7D7-D540-B541-D96D1CB8A35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://i.shgcdn.com/24292171-b6d0-4fe1-b487-3a840e214207/-/resize/1920x/</t>
   </si>
 </sst>
 </file>
@@ -791,6 +794,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" ht="23">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Esker Hayduke Ti 2025.xlsx
+++ b/data/gravel/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC373937-F7D7-D540-B541-D96D1CB8A35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4560CD7-83DC-DB49-AA7C-32B1EE9F9275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,12 @@
   </si>
   <si>
     <t>https://i.shgcdn.com/24292171-b6d0-4fe1-b487-3a840e214207/-/resize/1920x/</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -748,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1581,6 +1587,14 @@
         <v>109</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Esker Hayduke Ti 2025.xlsx
+++ b/data/gravel/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4560CD7-83DC-DB49-AA7C-32B1EE9F9275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E105A6-F75D-7B4C-BCDD-281C536C622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,24 @@
   </si>
   <si>
     <t>Minneapolis, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -754,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1430,168 +1448,198 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <v>31.6</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54">
-        <v>34</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="B60">
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B70">
-        <v>2500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71">
-        <v>4500</v>
+        <v>61</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>113</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>114</v>
       </c>
     </row>

--- a/data/gravel/Esker Hayduke Ti 2025.xlsx
+++ b/data/gravel/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E105A6-F75D-7B4C-BCDD-281C536C622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC790C-8A4F-BA49-8C8F-8C8BAF4935CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -245,9 +245,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -396,13 +393,22 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -415,13 +421,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Avenir Next"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Avenir Next"/>
@@ -446,6 +445,17 @@
       <name val="Avenir Next"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -467,15 +477,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,29 +783,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -802,7 +813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -810,240 +821,276 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="23">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="23">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="3">
+        <v>75</v>
+      </c>
+      <c r="C9" s="7">
         <v>597</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="7">
         <v>626</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="7">
         <v>649</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="7">
         <v>683</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="3">
+        <v>76</v>
+      </c>
+      <c r="C10" s="7">
         <v>420</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="7">
         <v>450</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="7">
         <v>470</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="7">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="3">
+        <v>77</v>
+      </c>
+      <c r="C11" s="7">
         <v>615</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="7">
         <v>620</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="7">
         <v>630</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="7">
         <v>645</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="3">
+        <v>78</v>
+      </c>
+      <c r="C12" s="7">
         <v>67.5</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="7">
         <v>67.5</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="7">
         <v>67.5</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="7">
         <v>67.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="3">
+        <v>79</v>
+      </c>
+      <c r="C13" s="7">
         <v>105</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="7">
         <v>110</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="7">
         <v>120</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="7">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="3">
+        <v>80</v>
+      </c>
+      <c r="C14" s="7">
         <v>74</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="7">
         <v>74</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="7">
         <v>74</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="7">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="7">
+        <v>380</v>
+      </c>
+      <c r="D15" s="7">
+        <v>435</v>
+      </c>
+      <c r="E15" s="7">
+        <v>485</v>
+      </c>
+      <c r="F15" s="7">
+        <v>530</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="3">
-        <v>380</v>
-      </c>
-      <c r="D15" s="3">
-        <v>435</v>
-      </c>
-      <c r="E15" s="3">
-        <v>485</v>
-      </c>
-      <c r="F15" s="3">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="C16" s="7">
         <v>280</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="7">
         <v>235</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="7">
         <v>385</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="7">
         <v>430</v>
       </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="7">
+        <v>440</v>
+      </c>
+      <c r="D17" s="7">
+        <v>440</v>
+      </c>
+      <c r="E17" s="7">
+        <v>440</v>
+      </c>
+      <c r="F17" s="7">
+        <v>440</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="3">
-        <v>440</v>
-      </c>
-      <c r="D17" s="3">
-        <v>440</v>
-      </c>
-      <c r="E17" s="3">
-        <v>440</v>
-      </c>
-      <c r="F17" s="3">
-        <v>440</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>99</v>
+      <c r="H17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1051,596 +1098,664 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="3">
+        <v>83</v>
+      </c>
+      <c r="C18" s="7">
         <v>44</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="7">
         <v>44</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="7">
         <v>44</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="7">
         <v>44</v>
       </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="3">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7">
         <v>495</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="7">
         <v>495</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="7">
         <v>495</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="7">
         <v>495</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="G19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="3">
+        <v>85</v>
+      </c>
+      <c r="C20" s="7">
         <v>65</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="7">
         <v>65</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="7">
         <v>65</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="7">
         <v>65</v>
       </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="3">
+        <v>86</v>
+      </c>
+      <c r="C21" s="7">
         <v>1130</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>1160</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>1183</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="7">
         <v>1218</v>
       </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="3">
+        <v>87</v>
+      </c>
+      <c r="C22" s="7">
         <v>50</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="7">
         <v>50</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="7">
         <v>50</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="7">
         <v>50</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B23" s="6"/>
-      <c r="D23" s="3">
+      <c r="C23" s="7">
+        <v>120</v>
+      </c>
+      <c r="D23" s="7">
+        <v>120</v>
+      </c>
+      <c r="E23" s="7">
+        <v>120</v>
+      </c>
+      <c r="F23" s="7">
+        <v>120</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7">
+        <v>30</v>
+      </c>
+      <c r="D24" s="7">
+        <v>30</v>
+      </c>
+      <c r="E24" s="7">
+        <v>30</v>
+      </c>
+      <c r="F24" s="7">
+        <v>30</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7">
         <v>2329</v>
       </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="1"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>22</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>24</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
-      </c>
-      <c r="F29">
-        <v>700</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>700</v>
+      </c>
+      <c r="D31">
+        <v>700</v>
+      </c>
+      <c r="E31">
+        <v>700</v>
+      </c>
+      <c r="F31">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:F30" si="0">2.6*25.4</f>
+      <c r="D32">
+        <f t="shared" ref="D32:F32" si="0">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <f>2.8*25.4</f>
         <v>71.11999999999999</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:F31" si="1">2.8*25.4</f>
+      <c r="D33">
+        <f t="shared" ref="D33:F33" si="1">2.8*25.4</f>
         <v>71.11999999999999</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>71.11999999999999</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="1"/>
         <v>71.11999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="D32">
-        <f>AVERAGE(D34,C35)*2.54</f>
+      <c r="D34">
+        <f>AVERAGE(D36,C37)*2.54</f>
         <v>168.91</v>
       </c>
-      <c r="E32">
-        <f t="shared" ref="E32:F32" si="2">AVERAGE(E34,D35)*2.54</f>
+      <c r="E34">
+        <f t="shared" ref="E34:F34" si="2">AVERAGE(E36,D37)*2.54</f>
         <v>176.53</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <f t="shared" si="2"/>
         <v>184.15</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="1">
-        <f>D32</f>
+      <c r="C35" s="1">
+        <f>D34</f>
         <v>168.91</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ref="D33:E33" si="3">E32</f>
+      <c r="D35" s="1">
+        <f t="shared" ref="D35:E35" si="3">E34</f>
         <v>176.53</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E35" s="1">
         <f t="shared" si="3"/>
         <v>184.15</v>
       </c>
-      <c r="F33">
-        <f t="shared" ref="F33" si="4">F35*2.54</f>
+      <c r="F35">
+        <f t="shared" ref="F35" si="4">F37*2.54</f>
         <v>193.04</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="C34">
+    <row r="36" spans="1:7">
+      <c r="C36">
         <v>63</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>66</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>69</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35">
-        <v>67</v>
-      </c>
-      <c r="D35">
-        <v>70</v>
-      </c>
-      <c r="E35">
-        <v>73</v>
-      </c>
-      <c r="F35">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37">
+        <v>67</v>
+      </c>
+      <c r="D37">
+        <v>70</v>
+      </c>
+      <c r="E37">
         <v>73</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>101</v>
+      <c r="F37">
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>111</v>
+        <v>70</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" t="s">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>36</v>
+        <v>73</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
         <v>38</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <f>2.8*25.4</f>
         <v>71.11999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
-      </c>
-    </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="1">
-        <v>120</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B46">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="B47" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49">
-        <v>110</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>45</v>
+      </c>
+      <c r="B51">
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58">
-        <v>31.6</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B60">
-        <v>34</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B62">
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76">
-        <v>2500</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77">
-        <v>4500</v>
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>36</v>
+        <v>66</v>
+      </c>
+      <c r="B78">
+        <v>2500</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>69</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>109</v>
+        <v>67</v>
+      </c>
+      <c r="B79">
+        <v>4500</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>69</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
         <v>113</v>
-      </c>
-      <c r="B80" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
